--- a/rtos-api-analysis/results/rt-thread_runtime_info_walltime.xlsx
+++ b/rtos-api-analysis/results/rt-thread_runtime_info_walltime.xlsx
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2671</v>
+        <v>0.1645</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.5908</v>
+        <v>1.3374</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4395</v>
+        <v>0.4387</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.2536</v>
+        <v>0.3808</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7456</v>
+        <v>1.0787</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.8435</v>
+        <v>4.0854</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2809</v>
+        <v>0.4097</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -823,7 +823,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.4912</v>
+        <v>0.593</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -871,7 +871,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.2897</v>
+        <v>0.3217</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.1487</v>
+        <v>2.4118</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.1972</v>
+        <v>0.2114</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.1961</v>
+        <v>0.1952</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1063,7 +1063,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7685999999999999</v>
+        <v>0.8428</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.1029</v>
+        <v>0.1094</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6054</v>
+        <v>0.8979</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5891999999999999</v>
+        <v>0.8075</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.0102</v>
+        <v>0.0142</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.2417</v>
+        <v>0.3613</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5984</v>
+        <v>0.636</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.9885</v>
+        <v>1.808</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1638</v>
+        <v>0.2958</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.1489</v>
+        <v>0.1161</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1159</v>
+        <v>0.1247</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.5975</v>
+        <v>2.2366</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1639,7 +1639,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0201</v>
+        <v>0.0449</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7738</v>
+        <v>1.0397</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0556</v>
+        <v>0.0927</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.3821</v>
+        <v>0.5077</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.274</v>
+        <v>0.3166</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0391</v>
+        <v>0.0805</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1927,7 +1927,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.0291</v>
+        <v>0.0654</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.3102</v>
+        <v>0.6146</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8505</v>
+        <v>0.976</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>49.2585</v>
+        <v>120.6312</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.895</v>
+        <v>1.1926</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.2991</v>
+        <v>0.3682</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>35.4213</v>
+        <v>57.1535</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.1022</v>
+        <v>0.0659</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>24.1049</v>
+        <v>33.7748</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.4303</v>
+        <v>0.5115</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.8191</v>
+        <v>2.7319</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -2455,7 +2455,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.1379</v>
+        <v>0.1361</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.0552</v>
+        <v>0.0376</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.2678</v>
+        <v>0.1943</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.0497</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3.2977</v>
+        <v>3.2782</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.102</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2743,7 +2743,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6225000000000001</v>
+        <v>0.7708</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2.5483</v>
+        <v>3.0345</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.0413</v>
+        <v>0.0357</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2935,7 +2935,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7828000000000001</v>
+        <v>0.8306</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>5.711</v>
+        <v>6.5058</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.1239</v>
+        <v>0.1517</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>12.3146</v>
+        <v>18.8403</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.0027</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5741000000000001</v>
+        <v>0.8053</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -3223,7 +3223,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>84.93000000000001</v>
+        <v>264.4782</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.372</v>
+        <v>0.4238</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6494</v>
+        <v>0.9517</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.0295</v>
+        <v>0.0325</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.0299</v>
+        <v>0.0377</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.3363</v>
+        <v>0.3124</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -3511,7 +3511,7 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>431.2928</v>
+        <v>780.2226000000001</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -3519,21 +3519,21 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>0.208</v>
+        <v>0.2067</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2183</t>
+          <t>2174</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>540138</t>
+          <t>537721</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2183</t>
+          <t>2174</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -3559,7 +3559,7 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>84.8167</v>
+        <v>229.0649</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -3607,7 +3607,7 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>11.5861</v>
+        <v>16.0108</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7232</v>
+        <v>0.6802</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.1785</v>
+        <v>0.1767</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.6181</v>
+        <v>0.7471</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>11.5407</v>
+        <v>18.9919</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -3807,21 +3807,21 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0.2572</v>
+        <v>0.2601</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>4099</t>
+          <t>4133</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -3847,7 +3847,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>4.9799</v>
+        <v>5.6309</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5931</v>
+        <v>0.6882</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.0891</v>
+        <v>0.1231</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.1733</v>
+        <v>0.0237</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.1513</v>
+        <v>0.1564</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.6209</v>
+        <v>0.6341</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -4135,7 +4135,7 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.0501</v>
+        <v>0.0634</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.2625</v>
+        <v>0.3228</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -4231,7 +4231,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>87.7116</v>
+        <v>258.4822</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -4279,7 +4279,7 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.2045</v>
+        <v>0.2105</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -4327,7 +4327,7 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.0466</v>
+        <v>0.0478</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>3.2359</v>
+        <v>3.6073</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -4423,7 +4423,7 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.1261</v>
+        <v>0.1157</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -4471,7 +4471,7 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.0516</v>
+        <v>0.0497</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>15.6672</v>
+        <v>26.1315</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.3064</v>
+        <v>0.2319</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.0022</v>
+        <v>0.0133</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.0059</v>
+        <v>0.0158</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -4711,7 +4711,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4672</v>
+        <v>0.5031</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.2464</v>
+        <v>0.2803</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.9093</v>
+        <v>0.9923</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -4855,7 +4855,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.0023</v>
+        <v>0.0092</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -4903,7 +4903,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.2918</v>
+        <v>0.3208</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>55.4564</v>
+        <v>95.4601</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>15.175</v>
+        <v>26.1802</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -5047,7 +5047,7 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5856</v>
+        <v>0.7634</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>54.5984</v>
+        <v>95.0676</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.2349</v>
+        <v>0.2341</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -5191,7 +5191,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1.3131</v>
+        <v>1.3189</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -5239,7 +5239,7 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.3585</v>
+        <v>0.4102</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.0086</v>
+        <v>0.0078</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -5335,7 +5335,7 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.0549</v>
+        <v>0.0897</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.2347</v>
+        <v>0.264</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -5431,7 +5431,7 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.4165</v>
+        <v>0.387</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -5479,7 +5479,7 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.153</v>
+        <v>0.1116</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>2.8125</v>
+        <v>3.2525</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.1096</v>
+        <v>0.1347</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -5623,7 +5623,7 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.0641</v>
+        <v>0.079</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.0389</v>
+        <v>0.0424</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.4515</v>
+        <v>0.4675</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1.2381</v>
+        <v>1.696</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.1822</v>
+        <v>0.2411</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.0553</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.6532</v>
+        <v>0.5789</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>83.18559999999999</v>
+        <v>386.8334</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -5967,21 +5967,21 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>0.2362</v>
+        <v>0.233</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>143833</t>
+          <t>141180</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -6007,7 +6007,7 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.743</v>
+        <v>0.8467</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -6055,7 +6055,7 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.7197</v>
+        <v>0.6485</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.4791</v>
+        <v>0.5249</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5799</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.0177</v>
+        <v>0.0353</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5393</v>
+        <v>0.5482</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.3389</v>
+        <v>0.4157</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.2226</v>
+        <v>0.3496</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.4182</v>
+        <v>0.5375</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>35.027</v>
+        <v>43.4364</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -6487,7 +6487,7 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>121.0867</v>
+        <v>552.3599</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -6495,21 +6495,21 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>0.151</v>
+        <v>0.1493</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>145425</t>
+          <t>143448</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -6519,7 +6519,7 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -6535,7 +6535,7 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.6691</v>
+        <v>0.7751</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>1.5482</v>
+        <v>1.501</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -6631,7 +6631,7 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.6034</v>
+        <v>0.4834</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.4279</v>
+        <v>0.2356</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -6727,7 +6727,7 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>1.1836</v>
+        <v>1.3055</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -6775,7 +6775,7 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.1027</v>
+        <v>0.1149</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>36.4366</v>
+        <v>58.2006</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -6871,7 +6871,7 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.3286</v>
+        <v>0.361</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.0119</v>
+        <v>0.0092</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -6967,7 +6967,7 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>2.8243</v>
+        <v>3.3939</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -7015,7 +7015,7 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5046</v>
+        <v>0.5622</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -7063,7 +7063,7 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.1995</v>
+        <v>0.2173</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.4618</v>
+        <v>0.4963</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>2.3124</v>
+        <v>2.232</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.2561</v>
+        <v>0.4623</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.9583</v>
+        <v>1.8926</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.0022</v>
+        <v>0.0143</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5229</v>
+        <v>0.5317</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -7399,7 +7399,7 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.1427</v>
+        <v>0.1395</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.3332</v>
+        <v>0.4065</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.356</v>
+        <v>0.3862</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.1459</v>
+        <v>0.1081</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -7591,7 +7591,7 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.2398</v>
+        <v>0.2718</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.4786</v>
+        <v>0.3598</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -7687,7 +7687,7 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.2998</v>
+        <v>0.2336</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -7735,7 +7735,7 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.0227</v>
+        <v>0.0902</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.1562</v>
+        <v>0.1465</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.2432</v>
+        <v>0.3022</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>1.0987</v>
+        <v>1.7502</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -7927,7 +7927,7 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>69.7734</v>
+        <v>89.6557</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>0.0626</v>
+        <v>0.0769</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>36000.6306</v>
+        <v>36000.6487</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>240068</t>
+          <t>233940</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -8071,7 +8071,7 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.3024</v>
+        <v>0.2445</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.5634</v>
+        <v>0.8247</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>1.2921</v>
+        <v>0.9504</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>69.2307</v>
+        <v>265.4143</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -8223,21 +8223,21 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>0.0605</v>
+        <v>0.0621</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>100260</t>
+          <t>100812</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -8247,7 +8247,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>47</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -8263,7 +8263,7 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.2481</v>
+        <v>0.4356</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -8311,7 +8311,7 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>86.904</v>
+        <v>268.4545</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.8438</v>
+        <v>1.089</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -8407,7 +8407,7 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.1224</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -8455,7 +8455,7 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.0252</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.0488</v>
+        <v>0.053</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.0733</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>0.0906</v>
+        <v>0.2694</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -8647,7 +8647,7 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>0.4859</v>
+        <v>0.5396</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>244.0841</v>
+        <v>503.197</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>4.8379</v>
+        <v>5.4606</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>0.0142</v>
+        <v>0.0293</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>0.5754</v>
+        <v>1.0315</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>0.0367</v>
+        <v>0.0606</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -8935,7 +8935,7 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>0.1264</v>
+        <v>0.1166</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -8983,7 +8983,7 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>1.0092</v>
+        <v>1.2791</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -9031,7 +9031,7 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>0.3695</v>
+        <v>0.338</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="B181" t="n">
-        <v>0.0027</v>
+        <v>0.017</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -9127,7 +9127,7 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>0.0954</v>
+        <v>0.0762</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>0.1646</v>
+        <v>0.0755</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>0.3563</v>
+        <v>0.3316</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>51.8582</v>
+        <v>101.5556</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>0.002</v>
+        <v>0.0021</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0.5338000000000001</v>
+        <v>0.633</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -9415,7 +9415,7 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>3.0347</v>
+        <v>3.1788</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -9463,7 +9463,7 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>12.9544</v>
+        <v>16.2014</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -9511,7 +9511,7 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>86.13079999999999</v>
+        <v>257.2738</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -9559,7 +9559,7 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>0.4741</v>
+        <v>0.4995</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>0.009299999999999999</v>
+        <v>0.0074</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -9655,7 +9655,7 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>0.0534</v>
+        <v>0.0578</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>0.2661</v>
+        <v>0.2989</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>0.1098</v>
+        <v>0.1077</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>0.0771</v>
+        <v>0.0953</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>0.2408</v>
+        <v>0.265</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -9895,7 +9895,7 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>0.5141</v>
+        <v>0.6837</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -9943,7 +9943,7 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>0.032</v>
+        <v>0.0606</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -9991,7 +9991,7 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>89.3904</v>
+        <v>271.8696</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>36000.3119</v>
+        <v>36000.4899</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -10056,7 +10056,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>334720</t>
+          <t>325755</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -10087,7 +10087,7 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>0.002</v>
+        <v>0.0121</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -10135,7 +10135,7 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>0.4009</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -10183,7 +10183,7 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>15.9897</v>
+        <v>25.727</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -10231,7 +10231,7 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>3.1439</v>
+        <v>3.2344</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0.0917</v>
+        <v>0.0738</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
